--- a/product_selector_out/STM32WBx5 - diff.xlsx
+++ b/product_selector_out/STM32WBx5 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7E1CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,13 +81,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -531,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -591,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -601,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -611,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="18">
@@ -833,18 +851,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3||5</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -856,59 +878,67 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3, 5</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WB55VE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3||5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WB55VE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -920,18 +950,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32WB55RE</t>
+          <t>STM32WB55VE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -943,18 +973,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32WB55RE</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -966,18 +996,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -989,18 +1019,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55RE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1012,18 +1042,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32WB55CG</t>
+          <t>STM32WB55RE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1035,76 +1065,88 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32WB55CG</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3||5</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32WB55RG</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3, 5</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32WB55RG</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3||5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32WB35CE</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1127,7 +1169,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32WB35CE</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1150,7 +1192,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32WB35CC</t>
+          <t>STM32WB55CG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1173,7 +1215,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32WB35CC</t>
+          <t>STM32WB55CG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1196,7 +1238,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32WB55CE</t>
+          <t>STM32WB55RG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1219,7 +1261,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32WB55CE</t>
+          <t>STM32WB55RG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1239,8 +1281,146 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32WB35CE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32WB35CE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32WB35CC</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32WB35CC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E44"/>
+  <autoFilter ref="A18:E50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32WBx5 - diff.xlsx
+++ b/product_selector_out/STM32WBx5 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,21 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B7E1CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,16 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +531,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +591,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +601,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="18">
@@ -851,22 +833,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>3||5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -878,67 +856,59 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>3, 5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32WB55VE</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>3||5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32WB55VE</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -950,18 +920,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32WB55VE</t>
+          <t>STM32WB55RE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -973,18 +943,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WB55RE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -996,18 +966,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1019,18 +989,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32WB55RE</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1042,18 +1012,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32WB55RE</t>
+          <t>STM32WB55CG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1065,88 +1035,76 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55CG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>3||5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55RG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>3, 5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55RG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>3||5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB35CE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1169,7 +1127,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB35CE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1192,7 +1150,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32WB55CG</t>
+          <t>STM32WB35CC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1215,7 +1173,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32WB55CG</t>
+          <t>STM32WB35CC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1238,7 +1196,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32WB55RG</t>
+          <t>STM32WB55CE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1261,7 +1219,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32WB55RG</t>
+          <t>STM32WB55CE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1281,146 +1239,8 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A18:E50"/>
+  <autoFilter ref="A18:E44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32WBx5 - diff.xlsx
+++ b/product_selector_out/STM32WBx5 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>871</v>
+        <v>884</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>845</v>
+        <v>857</v>
       </c>
     </row>
     <row r="18">
@@ -920,18 +920,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32WB55RE</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -948,13 +948,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -966,18 +966,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32WB55VC</t>
+          <t>STM32WB55RE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -994,13 +994,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1012,18 +1012,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32WB55CG</t>
+          <t>STM32WB55VC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1040,13 +1040,13 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1058,18 +1058,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32WB55RG</t>
+          <t>STM32WB55CG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1086,13 +1086,13 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1104,18 +1104,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32WB35CE</t>
+          <t>STM32WB55RG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1132,13 +1132,13 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -1150,18 +1150,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32WB35CC</t>
+          <t>STM32WB35CE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1178,13 +1178,13 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -1196,18 +1196,18 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32WB55CE</t>
+          <t>STM32WB35CC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -1224,23 +1224,46 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E44"/>
+  <autoFilter ref="A18:E45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>